--- a/Employee_Reports_wi48/Jeffrey Manarpaac Urolaza Q0503.xlsx
+++ b/Employee_Reports_wi48/Jeffrey Manarpaac Urolaza Q0503.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1390,11 +1390,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1439,11 +1439,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2076,11 +2076,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2125,11 +2125,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2174,11 +2174,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2211,11 +2211,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2309,11 +2309,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2346,11 +2346,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2395,11 +2395,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2516,9 +2516,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t>16-Dec-2025</t>
@@ -2530,11 +2542,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2579,11 +2591,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2628,11 +2640,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2677,11 +2689,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2714,11 +2726,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2763,11 +2775,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2800,11 +2812,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3223,7 +3235,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7814</v>
+        <v>7811</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
